--- a/tp_education_system/backend/services/exports/绩效工资审批表_2026年6月.xlsx
+++ b/tp_education_system/backend/services/exports/绩效工资审批表_2026年6月.xlsx
@@ -2216,18 +2216,31 @@
     <row r="1" ht="27" customFormat="1" customHeight="1" s="13">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>2026年5月 义务教育学校教职工绩效工资审批表</t>
-        </is>
-      </c>
-      <c r="B1" s="119" t="n">
-        <v>46170</v>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B1" s="119" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>义务教育学校教职工绩效工资审批表</t>
-        </is>
-      </c>
-      <c r="E1" s="38" t="n"/>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="E1" s="38" t="inlineStr">
+        <is>
+          <t>呈报单位意见</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>据实填写，同意呈报。
+              （盖章）
+              2026年5月1日</t>
+        </is>
+      </c>
       <c r="G1" s="7" t="n"/>
       <c r="H1" s="8" t="n"/>
       <c r="I1" s="8" t="n"/>
@@ -2237,7 +2250,7 @@
     <row r="2" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>填报单位： 太平镇中心学校 填报时间: 2026年4月28日 单位： 人、元</t>
+          <t>行政管理人员</t>
         </is>
       </c>
       <c r="B2" s="38" t="inlineStr">
@@ -2250,8 +2263,10 @@
           <t>填报时间:</t>
         </is>
       </c>
-      <c r="G2" s="120" t="n">
-        <v>46140</v>
+      <c r="G2" s="120" t="inlineStr">
+        <is>
+          <t>2026年5月1日</t>
+        </is>
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
@@ -2268,14 +2283,10 @@
     <row r="3" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A3" s="121" t="inlineStr">
         <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B3" s="30" t="inlineStr">
-        <is>
-          <t>人数</t>
-        </is>
-      </c>
+          <t>1、副处级</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="n"/>
       <c r="C3" s="122" t="n"/>
       <c r="D3" s="123" t="n"/>
       <c r="E3" s="124" t="inlineStr">
@@ -2283,11 +2294,7 @@
           <t>呈报单位意见</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
-        <is>
-          <t>据实填写，同意呈报。（盖章）2026年4月28日</t>
-        </is>
-      </c>
+      <c r="F3" s="49" t="n"/>
       <c r="G3" s="50" t="n"/>
       <c r="H3" s="50" t="n"/>
       <c r="I3" s="50" t="n"/>
@@ -2298,11 +2305,7 @@
       <c r="A4" s="125" t="n"/>
       <c r="B4" s="23" t="n"/>
       <c r="C4" s="23" t="n"/>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>小计</t>
-        </is>
-      </c>
+      <c r="D4" s="24" t="n"/>
       <c r="E4" s="126" t="n"/>
       <c r="F4" s="41" t="n"/>
       <c r="K4" s="42" t="n"/>
@@ -2310,7 +2313,7 @@
     <row r="5" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>1、副处级</t>
+          <t>3、副科级</t>
         </is>
       </c>
       <c r="B5" s="29" t="n"/>
@@ -2323,12 +2326,24 @@
     <row r="6" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>2、正科级</t>
-        </is>
-      </c>
-      <c r="B6" s="32" t="n"/>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="33" t="n"/>
+          <t>4、科员级</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>5925</t>
+        </is>
+      </c>
       <c r="E6" s="126" t="n"/>
       <c r="F6" s="127" t="inlineStr">
         <is>
@@ -2340,7 +2355,7 @@
     <row r="7" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>3、副科级</t>
+          <t>5、办事员级</t>
         </is>
       </c>
       <c r="B7" s="32" t="n"/>
@@ -2357,18 +2372,21 @@
     <row r="8" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>4、科员级</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>5925</v>
-      </c>
+          <t>专业技术人员</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>教育局意见</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>（盖章）
+              2026年5月2日</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="n"/>
       <c r="E8" s="126" t="n"/>
       <c r="F8" s="41" t="n"/>
       <c r="K8" s="42" t="n"/>
@@ -2376,11 +2394,15 @@
     <row r="9" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>5、办事员级</t>
+          <t>1、正高级</t>
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
-      <c r="C9" s="40" t="n"/>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="126" t="n"/>
       <c r="F9" s="41" t="n"/>
@@ -2393,20 +2415,24 @@
     <row r="10" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A10" s="43" t="inlineStr">
         <is>
-          <t>专业技术人员</t>
+          <t>2、高级教师</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>教育局意见</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>（盖章）2026年4月29日</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="n"/>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>67012</t>
+        </is>
+      </c>
       <c r="E10" s="125" t="n"/>
       <c r="F10" s="130" t="n">
         <v>46140</v>
@@ -2420,14 +2446,24 @@
     <row r="11" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A11" s="48" t="inlineStr">
         <is>
-          <t>1、正高级</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n"/>
-      <c r="C11" s="29" t="n">
-        <v>1862</v>
-      </c>
-      <c r="D11" s="30" t="n"/>
+          <t>3、一级教师</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>178024</t>
+        </is>
+      </c>
       <c r="E11" s="124" t="inlineStr">
         <is>
           <t>教育局意见</t>
@@ -2443,17 +2479,23 @@
     <row r="12" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>2、高级教师</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="n">
-        <v>44</v>
-      </c>
-      <c r="C12" s="40" t="n">
-        <v>1523</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>67012</v>
+          <t>4、二级教师</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>186150</t>
+        </is>
       </c>
       <c r="E12" s="126" t="n"/>
       <c r="F12" s="41" t="n"/>
@@ -2462,17 +2504,23 @@
     <row r="13" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A13" s="52" t="inlineStr">
         <is>
-          <t>3、一级教师</t>
-        </is>
-      </c>
-      <c r="B13" s="53" t="n">
-        <v>136</v>
-      </c>
-      <c r="C13" s="54" t="n">
-        <v>1309</v>
-      </c>
-      <c r="D13" s="55" t="n">
-        <v>178024</v>
+          <t>5、三级教师</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>21432</t>
+        </is>
       </c>
       <c r="E13" s="126" t="n"/>
       <c r="F13" s="41" t="n"/>
@@ -2492,17 +2540,17 @@
     <row r="14" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A14" s="57" t="inlineStr">
         <is>
-          <t>4、二级教师</t>
+          <t>工人</t>
         </is>
       </c>
       <c r="B14" s="53" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="C14" s="54" t="n">
-        <v>1241</v>
+        <v>1309</v>
       </c>
       <c r="D14" s="55" t="n">
-        <v>186150</v>
+        <v>178024</v>
       </c>
       <c r="E14" s="126" t="n"/>
       <c r="F14" s="41" t="n"/>
@@ -2511,18 +2559,12 @@
     <row r="15" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A15" s="57" t="inlineStr">
         <is>
-          <t>5、三级教师</t>
-        </is>
-      </c>
-      <c r="B15" s="53" t="n">
-        <v>19</v>
-      </c>
-      <c r="C15" s="54" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D15" s="55" t="n">
-        <v>21432</v>
-      </c>
+          <t>1、高级技师</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="n"/>
+      <c r="C15" s="54" t="n"/>
+      <c r="D15" s="55" t="n"/>
       <c r="E15" s="126" t="n"/>
       <c r="F15" s="129" t="inlineStr">
         <is>
@@ -2534,17 +2576,23 @@
     <row r="16" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A16" s="58" t="inlineStr">
         <is>
-          <t>工人</t>
-        </is>
-      </c>
-      <c r="B16" s="59" t="n">
-        <v>19</v>
-      </c>
-      <c r="C16" s="60" t="n">
-        <v>1128</v>
-      </c>
-      <c r="D16" s="99" t="n">
-        <v>21432</v>
+          <t>2、技师</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="D16" s="99" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
       </c>
       <c r="E16" s="126" t="n"/>
       <c r="F16" s="41" t="n"/>
@@ -2553,31 +2601,44 @@
     <row r="17" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A17" s="62" t="inlineStr">
         <is>
-          <t>1、高级技师</t>
+          <t>3、高级工</t>
         </is>
       </c>
       <c r="B17" s="63" t="n"/>
-      <c r="C17" s="63" t="n"/>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
       <c r="D17" s="64" t="n"/>
       <c r="E17" s="126" t="n"/>
-      <c r="F17" s="41" t="n"/>
+      <c r="F17" s="41" t="inlineStr">
+        <is>
+          <t>根据相关文件及有关规定，经审核，同意你单位：
+                基础性绩效工资357人，462311元；
+                生活补贴356人，124600元；
+                合计586911元；
+                岗位设置遗留2人，675.24元；
+                总计587586.24元。
+                无乡镇补贴1人，柯坤。
+              2026年5月2日</t>
+        </is>
+      </c>
       <c r="K17" s="42" t="n"/>
     </row>
     <row r="18" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A18" s="52" t="inlineStr">
         <is>
-          <t>2、技师</t>
-        </is>
-      </c>
-      <c r="B18" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="53" t="n">
-        <v>1331</v>
-      </c>
-      <c r="D18" s="55" t="n">
-        <v>2662</v>
-      </c>
+          <t>4、中级工</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="n"/>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
+      </c>
+      <c r="D18" s="55" t="n"/>
       <c r="E18" s="126" t="n"/>
       <c r="F18" s="41" t="n"/>
       <c r="K18" s="42" t="n"/>
@@ -2585,19 +2646,27 @@
     <row r="19" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A19" s="52" t="inlineStr">
         <is>
-          <t>3、高级工</t>
-        </is>
-      </c>
-      <c r="B19" s="53" t="n"/>
-      <c r="C19" s="54" t="n">
-        <v>1219</v>
-      </c>
-      <c r="D19" s="55" t="n"/>
+          <t>5、初级工</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D19" s="55" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
       <c r="E19" s="125" t="n"/>
-      <c r="F19" s="133" t="inlineStr">
-        <is>
-          <t>根据相关文件及有关规定，经审核，同意你单位：基础性绩效工资0人，0元；生活补贴0人，0元；合计0人，0元；岗位设置遗留0人，0元；总计0人，0元。无乡镇补贴0人，姓名。2026年4月29日</t>
-        </is>
+      <c r="F19" s="133" t="n">
+        <v>46141</v>
       </c>
       <c r="G19" s="131" t="n"/>
       <c r="H19" s="131" t="n"/>
@@ -2608,13 +2677,11 @@
     <row r="20" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A20" s="52" t="inlineStr">
         <is>
-          <t>4、中级工</t>
+          <t>6、普工</t>
         </is>
       </c>
       <c r="B20" s="53" t="n"/>
-      <c r="C20" s="54" t="n">
-        <v>1185</v>
-      </c>
+      <c r="C20" s="54" t="n"/>
       <c r="D20" s="55" t="n"/>
       <c r="E20" s="134" t="inlineStr">
         <is>
@@ -2635,17 +2702,19 @@
     <row r="21" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A21" s="52" t="inlineStr">
         <is>
-          <t>5、初级工</t>
-        </is>
-      </c>
-      <c r="B21" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="54" t="n">
-        <v>1106</v>
-      </c>
-      <c r="D21" s="55" t="n">
-        <v>1106</v>
+          <t>绩效工资合计</t>
+        </is>
+      </c>
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="55" t="inlineStr">
+        <is>
+          <t>462311</t>
+        </is>
       </c>
       <c r="E21" s="126" t="n"/>
       <c r="F21" s="73" t="inlineStr">
@@ -2673,12 +2742,24 @@
     <row r="22" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A22" s="52" t="inlineStr">
         <is>
-          <t>6、普工</t>
-        </is>
-      </c>
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="n"/>
+          <t>乡镇补贴合计</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="D22" s="55" t="inlineStr">
+        <is>
+          <t>124600</t>
+        </is>
+      </c>
       <c r="E22" s="126" t="n"/>
       <c r="F22" s="73" t="inlineStr">
         <is>
@@ -2705,18 +2786,30 @@
     <row r="23" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A23" s="58" t="inlineStr">
         <is>
-          <t>绩效工资合计</t>
-        </is>
-      </c>
-      <c r="B23" s="59" t="n">
-        <v>357</v>
-      </c>
-      <c r="C23" s="60" t="n"/>
-      <c r="D23" s="99" t="n">
-        <v>462311</v>
+          <t>岗位设置遗留问题</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>李发金</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
+      </c>
+      <c r="D23" s="99" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
       </c>
       <c r="E23" s="126" t="n"/>
-      <c r="F23" s="77" t="n"/>
+      <c r="F23" s="77" t="inlineStr">
+        <is>
+          <t>合计：</t>
+        </is>
+      </c>
       <c r="J23" s="79" t="n">
         <v>586911</v>
       </c>
@@ -2729,20 +2822,30 @@
     <row r="24" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A24" s="81" t="inlineStr">
         <is>
-          <t>乡镇补贴合计</t>
-        </is>
-      </c>
-      <c r="B24" s="82" t="n">
-        <v>356</v>
-      </c>
-      <c r="C24" s="82" t="n">
-        <v>350</v>
-      </c>
-      <c r="D24" s="83" t="n">
-        <v>124600</v>
+          <t>岗位设置遗留问题</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="inlineStr">
+        <is>
+          <t>李发金</t>
+        </is>
+      </c>
+      <c r="C24" s="82" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
+      </c>
+      <c r="D24" s="83" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
       </c>
       <c r="E24" s="126" t="n"/>
-      <c r="F24" s="73" t="n"/>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>岗位设置遗留</t>
+        </is>
+      </c>
       <c r="H24" s="75" t="n">
         <v>2</v>
       </c>
@@ -2763,22 +2866,26 @@
     <row r="25" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A25" s="84" t="inlineStr">
         <is>
-          <t>岗位设置遗留问题</t>
+          <t>岗位设置遗留问题合计</t>
         </is>
       </c>
       <c r="B25" s="85" t="inlineStr">
         <is>
-          <t>李发金</t>
-        </is>
-      </c>
-      <c r="C25" s="85" t="n">
-        <v>321.3</v>
-      </c>
-      <c r="D25" s="86" t="n">
-        <v>321.3</v>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C25" s="85" t="n"/>
+      <c r="D25" s="86" t="inlineStr">
+        <is>
+          <t>675.24</t>
+        </is>
       </c>
       <c r="E25" s="126" t="n"/>
-      <c r="F25" s="77" t="n"/>
+      <c r="F25" s="77" t="inlineStr">
+        <is>
+          <t>总计：</t>
+        </is>
+      </c>
       <c r="J25" s="79">
         <f>J23+J24</f>
         <v/>
@@ -2792,22 +2899,22 @@
     <row r="26" ht="37" customFormat="1" customHeight="1" s="13">
       <c r="A26" s="87" t="inlineStr">
         <is>
-          <t>岗位设置遗留问题</t>
+          <t>退休干部</t>
         </is>
       </c>
       <c r="B26" s="88" t="inlineStr">
         <is>
-          <t>李发金</t>
-        </is>
-      </c>
-      <c r="C26" s="89" t="n">
-        <v>321.3</v>
-      </c>
-      <c r="D26" s="90" t="n">
-        <v>321.3</v>
-      </c>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="C26" s="89" t="n"/>
+      <c r="D26" s="90" t="n"/>
       <c r="E26" s="126" t="n"/>
-      <c r="F26" s="73" t="n"/>
+      <c r="F26" s="73" t="inlineStr">
+        <is>
+          <t>无乡镇补贴</t>
+        </is>
+      </c>
       <c r="H26" s="75" t="n">
         <v>1</v>
       </c>
@@ -2826,16 +2933,16 @@
     <row r="27" ht="37" customFormat="1" customHeight="1" s="13">
       <c r="A27" s="104" t="inlineStr">
         <is>
-          <t>岗位设置遗留问题合计</t>
-        </is>
-      </c>
-      <c r="B27" s="94" t="n">
-        <v>2</v>
+          <t>退休工人</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C27" s="105" t="n"/>
-      <c r="D27" s="96" t="n">
-        <v>675.24</v>
-      </c>
+      <c r="D27" s="96" t="n"/>
       <c r="E27" s="126" t="n"/>
       <c r="F27" s="77" t="n"/>
       <c r="J27" s="79" t="n"/>
@@ -2844,11 +2951,13 @@
     <row r="28" ht="36" customFormat="1" customHeight="1" s="13">
       <c r="A28" s="97" t="inlineStr">
         <is>
-          <t>退休干部</t>
-        </is>
-      </c>
-      <c r="B28" s="98" t="n">
-        <v>449</v>
+          <t>离休干部</t>
+        </is>
+      </c>
+      <c r="B28" s="98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C28" s="59" t="n"/>
       <c r="D28" s="99" t="n"/>
@@ -2859,11 +2968,11 @@
     <row r="29" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A29" s="100" t="inlineStr">
         <is>
-          <t>退休工人</t>
+          <t>备注：</t>
         </is>
       </c>
       <c r="B29" s="101" t="n">
-        <v>2</v>
+        <v>447</v>
       </c>
       <c r="C29" s="102" t="n"/>
       <c r="D29" s="103" t="n"/>
@@ -2874,11 +2983,11 @@
     <row r="30" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A30" s="104" t="inlineStr">
         <is>
-          <t>离休干部</t>
+          <t>退休工人</t>
         </is>
       </c>
       <c r="B30" s="105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="53" t="n"/>
       <c r="D30" s="106" t="n"/>
@@ -2892,7 +3001,7 @@
     <row r="31" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A31" s="109" t="inlineStr">
         <is>
-          <t>备注：</t>
+          <t>离休干部</t>
         </is>
       </c>
       <c r="B31" s="98" t="n">

--- a/tp_education_system/backend/services/exports/绩效工资审批表_2026年6月.xlsx
+++ b/tp_education_system/backend/services/exports/绩效工资审批表_2026年6月.xlsx
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K21" s="76" t="inlineStr">
         <is>
-          <t>元；</t>
+          <t>2026年5月1日</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,11 @@
           <t>柯坤</t>
         </is>
       </c>
-      <c r="K26" s="76" t="n"/>
+      <c r="K26" s="76" t="inlineStr">
+        <is>
+          <t>2026年5月2日</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="37" customFormat="1" customHeight="1" s="13">
       <c r="A27" s="104" t="inlineStr">
@@ -3010,8 +3014,10 @@
       <c r="C31" s="59" t="n"/>
       <c r="D31" s="110" t="n"/>
       <c r="E31" s="125" t="n"/>
-      <c r="F31" s="138" t="n">
-        <v>46142</v>
+      <c r="F31" s="138" t="inlineStr">
+        <is>
+          <t>2026年5月2日</t>
+        </is>
       </c>
       <c r="G31" s="131" t="n"/>
       <c r="H31" s="131" t="n"/>

--- a/tp_education_system/backend/services/exports/绩效工资审批表_2026年6月.xlsx
+++ b/tp_education_system/backend/services/exports/绩效工资审批表_2026年6月.xlsx
@@ -2434,8 +2434,10 @@
         </is>
       </c>
       <c r="E10" s="125" t="n"/>
-      <c r="F10" s="130" t="n">
-        <v>46140</v>
+      <c r="F10" s="130" t="inlineStr">
+        <is>
+          <t>2026年5月2日</t>
+        </is>
       </c>
       <c r="G10" s="131" t="n"/>
       <c r="H10" s="131" t="n"/>
@@ -2665,8 +2667,10 @@
         </is>
       </c>
       <c r="E19" s="125" t="n"/>
-      <c r="F19" s="133" t="n">
-        <v>46141</v>
+      <c r="F19" s="133" t="inlineStr">
+        <is>
+          <t>2026年5月2日</t>
+        </is>
       </c>
       <c r="G19" s="131" t="n"/>
       <c r="H19" s="131" t="n"/>
@@ -2735,7 +2739,7 @@
       </c>
       <c r="K21" s="76" t="inlineStr">
         <is>
-          <t>2026年5月1日</t>
+          <t>元；</t>
         </is>
       </c>
     </row>
@@ -2928,11 +2932,7 @@
           <t>柯坤</t>
         </is>
       </c>
-      <c r="K26" s="76" t="inlineStr">
-        <is>
-          <t>2026年5月2日</t>
-        </is>
-      </c>
+      <c r="K26" s="76" t="n"/>
     </row>
     <row r="27" ht="37" customFormat="1" customHeight="1" s="13">
       <c r="A27" s="104" t="inlineStr">
